--- a/tanoshimi/docs/공정도(WBS).xlsx
+++ b/tanoshimi/docs/공정도(WBS).xlsx
@@ -2132,7 +2132,7 @@
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>결제/예약 잔재 테이블 정리(reservations 등 3종 제거)</t>
+          <t xml:space="preserve">결제/예약 잔재 테이블 정리 (reservations 등 3종 + trip_schedules.reservation_id 제거, migration_v21). 조기 완료.</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
-          <t>예정</t>
+          <t xml:space="preserve">완료</t>
         </is>
       </c>
       <c r="AC44" s="7" t="n"/>
